--- a/companies/alder-ridge/source-files/Shared/Operations/Project Forecasts/June26 - PM updates/PM ETC updates_6.29 530pm_COMBINED_v3.xlsx
+++ b/companies/alder-ridge/source-files/Shared/Operations/Project Forecasts/June26 - PM updates/PM ETC updates_6.29 530pm_COMBINED_v3.xlsx
@@ -2413,12 +2413,12 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Included in PM ETC?</t>
+          <t>PM Forecast Treatment</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Recommended June Treatment</t>
+          <t>Finance Review Status</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cost exposure excluded</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
         <is>
-          <t>Exclude from contract value; include $275k probable cost exposure in EAC</t>
+          <t>Pending controller assessment under signed WIP policy</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Disputed recovery netted</t>
         </is>
       </c>
       <c r="I7" s="10" t="inlineStr">
         <is>
-          <t>Do not net the recovery against forecast cost</t>
+          <t>Pending controller assessment under signed WIP policy</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
@@ -2557,12 +2557,12 @@
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Cost exposure excluded</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr">
         <is>
-          <t>Exclude revenue; include $210k probable cost exposure</t>
+          <t>Pending controller assessment under signed WIP policy</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Reflected in approved forecast</t>
         </is>
       </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
-          <t>Included in accounting-system approved change orders</t>
+          <t>Executed before cutoff</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
@@ -2653,12 +2653,12 @@
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Cost exposure excluded</t>
         </is>
       </c>
       <c r="I10" s="10" t="inlineStr">
         <is>
-          <t>Exclude revenue; include $45k close-out cost exposure</t>
+          <t>Pending controller assessment under signed WIP policy</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Cost exposure excluded</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr">
         <is>
-          <t>Exclude from June close</t>
+          <t>Pending controller assessment under signed WIP policy</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Reflected in approved forecast</t>
         </is>
       </c>
       <c r="I12" s="10" t="inlineStr">
         <is>
-          <t>Already included in current contract and cost budget</t>
+          <t>Executed before cutoff</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Reflected in approved forecast</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr">
         <is>
-          <t>Already included in current contract and cost budget</t>
+          <t>Executed before cutoff</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
